--- a/Database Module/SQL Data/BD_Field_Mapping.xlsx
+++ b/Database Module/SQL Data/BD_Field_Mapping.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Reuse Decisions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Spec to Database'!$A$1:$H$280</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Spec to Database'!$A$1:$H$296</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Client Master Prefill'!$A$1:$C$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Reuse Decisions'!$A$1:$D$12</definedName>
   </definedNames>
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(100) · NOT NULL</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="G122" s="11" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · CHECK</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="G125" s="11" t="inlineStr">
@@ -9689,12 +9689,12 @@
       <c r="D240" s="10" t="inlineStr"/>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>bd_user_roles.bd_role</t>
+          <t>bd_user_roles.role</t>
         </is>
       </c>
       <c r="F240" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · NOT NULL, CHECK</t>
+          <t>VARCHAR(30) · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr">
@@ -9749,12 +9749,12 @@
       <c r="D242" s="10" t="inlineStr"/>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>bd_user_roles.updated_at</t>
+          <t>bd_user_roles.assigned_by</t>
         </is>
       </c>
       <c r="F242" s="10" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ · NOT NULL, DEFAULT</t>
+          <t>UUID · FK profiles</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr">
@@ -9771,7 +9771,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog</t>
+          <t>bd_user_roles</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr"/>
@@ -9779,12 +9779,12 @@
       <c r="D243" s="10" t="inlineStr"/>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.id</t>
+          <t>bd_user_roles.updated_at</t>
         </is>
       </c>
       <c r="F243" s="10" t="inlineStr">
         <is>
-          <t>UUID · PK, DEFAULT</t>
+          <t>TIMESTAMPTZ · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G243" s="13" t="inlineStr">
@@ -9809,12 +9809,12 @@
       <c r="D244" s="10" t="inlineStr"/>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.service_code</t>
+          <t>bd_service_catalog.id</t>
         </is>
       </c>
       <c r="F244" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(50) · UNIQUE, NOT NULL</t>
+          <t>UUID · PK, DEFAULT</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr">
@@ -9839,12 +9839,12 @@
       <c r="D245" s="10" t="inlineStr"/>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.service_name</t>
+          <t>bd_service_catalog.service_code</t>
         </is>
       </c>
       <c r="F245" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(150) · UNIQUE, NOT NULL</t>
+          <t>VARCHAR(50) · UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="G245" s="13" t="inlineStr">
@@ -9869,12 +9869,12 @@
       <c r="D246" s="10" t="inlineStr"/>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.service_category</t>
+          <t>bd_service_catalog.service_name</t>
         </is>
       </c>
       <c r="F246" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(50) · NOT NULL</t>
+          <t>VARCHAR(150) · UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr">
@@ -9899,12 +9899,12 @@
       <c r="D247" s="10" t="inlineStr"/>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.default_billing_frequency</t>
+          <t>bd_service_catalog.service_category</t>
         </is>
       </c>
       <c r="F247" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · CHECK</t>
+          <t>VARCHAR(50) · NOT NULL</t>
         </is>
       </c>
       <c r="G247" s="13" t="inlineStr">
@@ -9929,12 +9929,12 @@
       <c r="D248" s="10" t="inlineStr"/>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.database_folder</t>
+          <t>bd_service_catalog.default_billing_frequency</t>
         </is>
       </c>
       <c r="F248" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>VARCHAR(30) · CHECK</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr">
@@ -9959,12 +9959,12 @@
       <c r="D249" s="10" t="inlineStr"/>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.is_active</t>
+          <t>bd_service_catalog.database_folder</t>
         </is>
       </c>
       <c r="F249" s="10" t="inlineStr">
         <is>
-          <t>BOOLEAN · NOT NULL, DEFAULT</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="G249" s="13" t="inlineStr">
@@ -9989,12 +9989,12 @@
       <c r="D250" s="10" t="inlineStr"/>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.sort_order</t>
+          <t>bd_service_catalog.is_active</t>
         </is>
       </c>
       <c r="F250" s="10" t="inlineStr">
         <is>
-          <t>INTEGER · NOT NULL, DEFAULT</t>
+          <t>BOOLEAN · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr">
@@ -10019,12 +10019,12 @@
       <c r="D251" s="10" t="inlineStr"/>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.created_at</t>
+          <t>bd_service_catalog.sort_order</t>
         </is>
       </c>
       <c r="F251" s="10" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ · NOT NULL, DEFAULT</t>
+          <t>INTEGER · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G251" s="13" t="inlineStr">
@@ -10049,7 +10049,7 @@
       <c r="D252" s="10" t="inlineStr"/>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>bd_service_catalog.updated_at</t>
+          <t>bd_service_catalog.created_at</t>
         </is>
       </c>
       <c r="F252" s="10" t="inlineStr">
@@ -10071,7 +10071,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>bd_leads</t>
+          <t>bd_service_catalog</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr"/>
@@ -10079,12 +10079,12 @@
       <c r="D253" s="10" t="inlineStr"/>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>bd_leads.mobile_normalized</t>
+          <t>bd_service_catalog.updated_at</t>
         </is>
       </c>
       <c r="F253" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · GENERATED</t>
+          <t>TIMESTAMPTZ · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G253" s="13" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="H253" s="10" t="inlineStr">
         <is>
-          <t>Generated: digits of country code + mobile, for duplicate checks.</t>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
         </is>
       </c>
     </row>
@@ -10109,12 +10109,12 @@
       <c r="D254" s="10" t="inlineStr"/>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>bd_leads.email_normalized</t>
+          <t>bd_leads.mobile_normalized</t>
         </is>
       </c>
       <c r="F254" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(255) · GENERATED</t>
+          <t>VARCHAR(30) · GENERATED</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr">
@@ -10124,14 +10124,14 @@
       </c>
       <c r="H254" s="10" t="inlineStr">
         <is>
-          <t>Generated: lower(trim(email)), for duplicate checks.</t>
+          <t>Generated: digits of country code + mobile, for duplicate checks.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>bd_quotations</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr"/>
@@ -10139,12 +10139,12 @@
       <c r="D255" s="10" t="inlineStr"/>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>bd_quotations.version_no</t>
+          <t>bd_leads.email_normalized</t>
         </is>
       </c>
       <c r="F255" s="10" t="inlineStr">
         <is>
-          <t>INTEGER · NOT NULL, CHECK, DEFAULT</t>
+          <t>VARCHAR(255) · GENERATED</t>
         </is>
       </c>
       <c r="G255" s="13" t="inlineStr">
@@ -10154,14 +10154,14 @@
       </c>
       <c r="H255" s="10" t="inlineStr">
         <is>
-          <t>Spec: preserve issued quotation versions.</t>
+          <t>Generated: lower(trim(email)), for duplicate checks.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>bd_quotations</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr"/>
@@ -10169,12 +10169,12 @@
       <c r="D256" s="10" t="inlineStr"/>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>bd_quotations.supersedes_quotation_id</t>
+          <t>bd_leads.acquired_on</t>
         </is>
       </c>
       <c r="F256" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK bd_quotations</t>
+          <t>DATE · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr">
@@ -10184,14 +10184,14 @@
       </c>
       <c r="H256" s="10" t="inlineStr">
         <is>
-          <t>Links a new version to the one it replaces.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>bd_quotations</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr"/>
@@ -10199,12 +10199,12 @@
       <c r="D257" s="10" t="inlineStr"/>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>bd_quotations.quotation_template_id</t>
+          <t>bd_leads.estimated_budget</t>
         </is>
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>UUID</t>
+          <t>NUMERIC(18,2) · CHECK</t>
         </is>
       </c>
       <c r="G257" s="13" t="inlineStr">
@@ -10214,14 +10214,14 @@
       </c>
       <c r="H257" s="10" t="inlineStr">
         <is>
-          <t>Freezone .docx template used (public.quotation_templates on the live CRM).</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr"/>
@@ -10229,12 +10229,12 @@
       <c r="D258" s="10" t="inlineStr"/>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.id</t>
+          <t>bd_leads.budget_currency</t>
         </is>
       </c>
       <c r="F258" s="10" t="inlineStr">
         <is>
-          <t>UUID · PK, DEFAULT</t>
+          <t>CHAR(3) · NOT NULL, CHECK, DEFAULT</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr">
@@ -10244,14 +10244,14 @@
       </c>
       <c r="H258" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr"/>
@@ -10259,12 +10259,12 @@
       <c r="D259" s="10" t="inlineStr"/>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.quotation_id</t>
+          <t>bd_leads.internal_notes</t>
         </is>
       </c>
       <c r="F259" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK bd_quotations, NOT NULL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G259" s="13" t="inlineStr">
@@ -10274,14 +10274,14 @@
       </c>
       <c r="H259" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr"/>
@@ -10289,12 +10289,12 @@
       <c r="D260" s="10" t="inlineStr"/>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.lead_service_id</t>
+          <t>bd_leads.no_followup_reason</t>
         </is>
       </c>
       <c r="F260" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK bd_lead_services</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr">
@@ -10304,14 +10304,14 @@
       </c>
       <c r="H260" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_leads</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr"/>
@@ -10319,12 +10319,12 @@
       <c r="D261" s="10" t="inlineStr"/>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.line_no</t>
+          <t>bd_leads.duplicate_override</t>
         </is>
       </c>
       <c r="F261" s="10" t="inlineStr">
         <is>
-          <t>INTEGER · NOT NULL, CHECK</t>
+          <t>BOOLEAN · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G261" s="13" t="inlineStr">
@@ -10334,14 +10334,14 @@
       </c>
       <c r="H261" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_quotations</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr"/>
@@ -10349,12 +10349,12 @@
       <c r="D262" s="10" t="inlineStr"/>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.description</t>
+          <t>bd_quotations.version_no</t>
         </is>
       </c>
       <c r="F262" s="10" t="inlineStr">
         <is>
-          <t>TEXT · NOT NULL</t>
+          <t>INTEGER · NOT NULL, CHECK, DEFAULT</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr">
@@ -10364,14 +10364,14 @@
       </c>
       <c r="H262" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Spec: preserve issued quotation versions.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_quotations</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr"/>
@@ -10379,12 +10379,12 @@
       <c r="D263" s="10" t="inlineStr"/>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.quantity</t>
+          <t>bd_quotations.supersedes_quotation_id</t>
         </is>
       </c>
       <c r="F263" s="10" t="inlineStr">
         <is>
-          <t>NUMERIC(12,2) · NOT NULL, CHECK, DEFAULT</t>
+          <t>UUID · FK bd_quotations</t>
         </is>
       </c>
       <c r="G263" s="13" t="inlineStr">
@@ -10394,14 +10394,14 @@
       </c>
       <c r="H263" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Links a new version to the one it replaces.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_quotations</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr"/>
@@ -10409,12 +10409,12 @@
       <c r="D264" s="10" t="inlineStr"/>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.unit_price</t>
+          <t>bd_quotations.quotation_template_id</t>
         </is>
       </c>
       <c r="F264" s="10" t="inlineStr">
         <is>
-          <t>NUMERIC(18,2) · NOT NULL, CHECK</t>
+          <t>UUID</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr">
@@ -10424,14 +10424,14 @@
       </c>
       <c r="H264" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Freezone .docx template used (public.quotation_templates on the live CRM).</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_lead_services</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr"/>
@@ -10439,12 +10439,12 @@
       <c r="D265" s="10" t="inlineStr"/>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.discount_amount</t>
+          <t>bd_lead_services.quantity_scope</t>
         </is>
       </c>
       <c r="F265" s="10" t="inlineStr">
         <is>
-          <t>NUMERIC(18,2) · NOT NULL, CHECK, DEFAULT</t>
+          <t>VARCHAR(255)</t>
         </is>
       </c>
       <c r="G265" s="13" t="inlineStr">
@@ -10454,14 +10454,14 @@
       </c>
       <c r="H265" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items</t>
+          <t>bd_lead_services</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr"/>
@@ -10469,12 +10469,12 @@
       <c r="D266" s="10" t="inlineStr"/>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.line_total</t>
+          <t>bd_lead_services.quotation_reference</t>
         </is>
       </c>
       <c r="F266" s="10" t="inlineStr">
         <is>
-          <t>NUMERIC(18,2) · NOT NULL, CHECK</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H266" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
@@ -10499,12 +10499,12 @@
       <c r="D267" s="10" t="inlineStr"/>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>bd_quotation_items.billing_frequency</t>
+          <t>bd_quotation_items.id</t>
         </is>
       </c>
       <c r="F267" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · CHECK</t>
+          <t>UUID · PK, DEFAULT</t>
         </is>
       </c>
       <c r="G267" s="13" t="inlineStr">
@@ -10521,7 +10521,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr"/>
@@ -10529,12 +10529,12 @@
       <c r="D268" s="10" t="inlineStr"/>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.id</t>
+          <t>bd_quotation_items.quotation_id</t>
         </is>
       </c>
       <c r="F268" s="10" t="inlineStr">
         <is>
-          <t>UUID · PK, DEFAULT</t>
+          <t>UUID · FK bd_quotations, NOT NULL</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr">
@@ -10551,7 +10551,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr"/>
@@ -10559,12 +10559,12 @@
       <c r="D269" s="10" t="inlineStr"/>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.followup_id</t>
+          <t>bd_quotation_items.lead_service_id</t>
         </is>
       </c>
       <c r="F269" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK bd_followups, NOT NULL</t>
+          <t>UUID · FK bd_lead_services</t>
         </is>
       </c>
       <c r="G269" s="13" t="inlineStr">
@@ -10581,7 +10581,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr"/>
@@ -10589,12 +10589,12 @@
       <c r="D270" s="10" t="inlineStr"/>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.action</t>
+          <t>bd_quotation_items.line_no</t>
         </is>
       </c>
       <c r="F270" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · NOT NULL, CHECK</t>
+          <t>INTEGER · NOT NULL, CHECK</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr">
@@ -10611,7 +10611,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr"/>
@@ -10619,12 +10619,12 @@
       <c r="D271" s="10" t="inlineStr"/>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.previous_scheduled_at</t>
+          <t>bd_quotation_items.description</t>
         </is>
       </c>
       <c r="F271" s="10" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT · NOT NULL</t>
         </is>
       </c>
       <c r="G271" s="13" t="inlineStr">
@@ -10641,7 +10641,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr"/>
@@ -10649,12 +10649,12 @@
       <c r="D272" s="10" t="inlineStr"/>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.new_scheduled_at</t>
+          <t>bd_quotation_items.quantity</t>
         </is>
       </c>
       <c r="F272" s="10" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>NUMERIC(12,2) · NOT NULL, CHECK, DEFAULT</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr"/>
@@ -10679,12 +10679,12 @@
       <c r="D273" s="10" t="inlineStr"/>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.previous_assignee_id</t>
+          <t>bd_quotation_items.unit_price</t>
         </is>
       </c>
       <c r="F273" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK profiles</t>
+          <t>NUMERIC(18,2) · NOT NULL, CHECK</t>
         </is>
       </c>
       <c r="G273" s="13" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr"/>
@@ -10709,12 +10709,12 @@
       <c r="D274" s="10" t="inlineStr"/>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.new_assignee_id</t>
+          <t>bd_quotation_items.discount_amount</t>
         </is>
       </c>
       <c r="F274" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK profiles</t>
+          <t>NUMERIC(18,2) · NOT NULL, CHECK, DEFAULT</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr">
@@ -10731,7 +10731,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr"/>
@@ -10739,12 +10739,12 @@
       <c r="D275" s="10" t="inlineStr"/>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.reason</t>
+          <t>bd_quotation_items.line_total</t>
         </is>
       </c>
       <c r="F275" s="10" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>NUMERIC(18,2) · NOT NULL, CHECK</t>
         </is>
       </c>
       <c r="G275" s="13" t="inlineStr">
@@ -10761,7 +10761,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_quotation_items</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr"/>
@@ -10769,12 +10769,12 @@
       <c r="D276" s="10" t="inlineStr"/>
       <c r="E276" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.changed_by_user_id</t>
+          <t>bd_quotation_items.billing_frequency</t>
         </is>
       </c>
       <c r="F276" s="10" t="inlineStr">
         <is>
-          <t>UUID · FK profiles, NOT NULL</t>
+          <t>VARCHAR(30) · CHECK</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr">
@@ -10791,7 +10791,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history</t>
+          <t>bd_discussions</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr"/>
@@ -10799,12 +10799,12 @@
       <c r="D277" s="10" t="inlineStr"/>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>bd_followup_history.changed_at</t>
+          <t>bd_discussions.channel_detail</t>
         </is>
       </c>
       <c r="F277" s="10" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ · NOT NULL, DEFAULT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="G277" s="13" t="inlineStr">
@@ -10814,14 +10814,14 @@
       </c>
       <c r="H277" s="10" t="inlineStr">
         <is>
-          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>bd_lead_stage_history</t>
+          <t>bd_discussions</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr"/>
@@ -10829,12 +10829,12 @@
       <c r="D278" s="10" t="inlineStr"/>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>bd_lead_stage_history.from_status</t>
+          <t>bd_discussions.services_discussed</t>
         </is>
       </c>
       <c r="F278" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>TEXT · NOT NULL, DEFAULT</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr">
@@ -10844,14 +10844,14 @@
       </c>
       <c r="H278" s="10" t="inlineStr">
         <is>
-          <t>Status at the transition, so Won/Lost/Reopen show in the same history.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>bd_lead_stage_history</t>
+          <t>bd_followups</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr"/>
@@ -10859,12 +10859,12 @@
       <c r="D279" s="10" t="inlineStr"/>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>bd_lead_stage_history.to_status</t>
+          <t>bd_followups.channel_detail</t>
         </is>
       </c>
       <c r="F279" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(30) · NOT NULL</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="G279" s="13" t="inlineStr">
@@ -10874,14 +10874,14 @@
       </c>
       <c r="H279" s="10" t="inlineStr">
         <is>
-          <t>Status after the transition.</t>
+          <t>Added</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>bd_onboarding_handovers</t>
+          <t>bd_followups</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr"/>
@@ -10889,29 +10889,509 @@
       <c r="D280" s="10" t="inlineStr"/>
       <c r="E280" s="9" t="inlineStr">
         <is>
+          <t>bd_followups.previous_outcome</t>
+        </is>
+      </c>
+      <c r="F280" s="10" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G280" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H280" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="inlineStr"/>
+      <c r="C281" s="9" t="inlineStr"/>
+      <c r="D281" s="10" t="inlineStr"/>
+      <c r="E281" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.id</t>
+        </is>
+      </c>
+      <c r="F281" s="10" t="inlineStr">
+        <is>
+          <t>UUID · PK, DEFAULT</t>
+        </is>
+      </c>
+      <c r="G281" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H281" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B282" s="9" t="inlineStr"/>
+      <c r="C282" s="9" t="inlineStr"/>
+      <c r="D282" s="10" t="inlineStr"/>
+      <c r="E282" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.followup_id</t>
+        </is>
+      </c>
+      <c r="F282" s="10" t="inlineStr">
+        <is>
+          <t>UUID · FK bd_followups, NOT NULL</t>
+        </is>
+      </c>
+      <c r="G282" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H282" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B283" s="9" t="inlineStr"/>
+      <c r="C283" s="9" t="inlineStr"/>
+      <c r="D283" s="10" t="inlineStr"/>
+      <c r="E283" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.action</t>
+        </is>
+      </c>
+      <c r="F283" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(30) · NOT NULL, CHECK</t>
+        </is>
+      </c>
+      <c r="G283" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H283" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B284" s="9" t="inlineStr"/>
+      <c r="C284" s="9" t="inlineStr"/>
+      <c r="D284" s="10" t="inlineStr"/>
+      <c r="E284" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.previous_scheduled_at</t>
+        </is>
+      </c>
+      <c r="F284" s="10" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G284" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H284" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B285" s="9" t="inlineStr"/>
+      <c r="C285" s="9" t="inlineStr"/>
+      <c r="D285" s="10" t="inlineStr"/>
+      <c r="E285" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.new_scheduled_at</t>
+        </is>
+      </c>
+      <c r="F285" s="10" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G285" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H285" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B286" s="9" t="inlineStr"/>
+      <c r="C286" s="9" t="inlineStr"/>
+      <c r="D286" s="10" t="inlineStr"/>
+      <c r="E286" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.previous_assignee_id</t>
+        </is>
+      </c>
+      <c r="F286" s="10" t="inlineStr">
+        <is>
+          <t>UUID · FK profiles</t>
+        </is>
+      </c>
+      <c r="G286" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H286" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B287" s="9" t="inlineStr"/>
+      <c r="C287" s="9" t="inlineStr"/>
+      <c r="D287" s="10" t="inlineStr"/>
+      <c r="E287" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.new_assignee_id</t>
+        </is>
+      </c>
+      <c r="F287" s="10" t="inlineStr">
+        <is>
+          <t>UUID · FK profiles</t>
+        </is>
+      </c>
+      <c r="G287" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H287" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B288" s="9" t="inlineStr"/>
+      <c r="C288" s="9" t="inlineStr"/>
+      <c r="D288" s="10" t="inlineStr"/>
+      <c r="E288" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.reason</t>
+        </is>
+      </c>
+      <c r="F288" s="10" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G288" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H288" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B289" s="9" t="inlineStr"/>
+      <c r="C289" s="9" t="inlineStr"/>
+      <c r="D289" s="10" t="inlineStr"/>
+      <c r="E289" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.changed_by_user_id</t>
+        </is>
+      </c>
+      <c r="F289" s="10" t="inlineStr">
+        <is>
+          <t>UUID · FK profiles, NOT NULL</t>
+        </is>
+      </c>
+      <c r="G289" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H289" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history</t>
+        </is>
+      </c>
+      <c r="B290" s="9" t="inlineStr"/>
+      <c r="C290" s="9" t="inlineStr"/>
+      <c r="D290" s="10" t="inlineStr"/>
+      <c r="E290" s="9" t="inlineStr">
+        <is>
+          <t>bd_followup_history.changed_at</t>
+        </is>
+      </c>
+      <c r="F290" s="10" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ · NOT NULL, DEFAULT</t>
+        </is>
+      </c>
+      <c r="G290" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H290" s="10" t="inlineStr">
+        <is>
+          <t>Supporting table (not one of the 13 spec tables): see Reuse Decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="9" t="inlineStr">
+        <is>
+          <t>bd_lead_stage_history</t>
+        </is>
+      </c>
+      <c r="B291" s="9" t="inlineStr"/>
+      <c r="C291" s="9" t="inlineStr"/>
+      <c r="D291" s="10" t="inlineStr"/>
+      <c r="E291" s="9" t="inlineStr">
+        <is>
+          <t>bd_lead_stage_history.from_status</t>
+        </is>
+      </c>
+      <c r="F291" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="G291" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H291" s="10" t="inlineStr">
+        <is>
+          <t>Status at the transition, so Won/Lost/Reopen show in the same history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="9" t="inlineStr">
+        <is>
+          <t>bd_lead_stage_history</t>
+        </is>
+      </c>
+      <c r="B292" s="9" t="inlineStr"/>
+      <c r="C292" s="9" t="inlineStr"/>
+      <c r="D292" s="10" t="inlineStr"/>
+      <c r="E292" s="9" t="inlineStr">
+        <is>
+          <t>bd_lead_stage_history.to_status</t>
+        </is>
+      </c>
+      <c r="F292" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(30) · NOT NULL</t>
+        </is>
+      </c>
+      <c r="G292" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H292" s="10" t="inlineStr">
+        <is>
+          <t>Status after the transition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers</t>
+        </is>
+      </c>
+      <c r="B293" s="9" t="inlineStr"/>
+      <c r="C293" s="9" t="inlineStr"/>
+      <c r="D293" s="10" t="inlineStr"/>
+      <c r="E293" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers.confirmation_contact</t>
+        </is>
+      </c>
+      <c r="F293" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="G293" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H293" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers</t>
+        </is>
+      </c>
+      <c r="B294" s="9" t="inlineStr"/>
+      <c r="C294" s="9" t="inlineStr"/>
+      <c r="D294" s="10" t="inlineStr"/>
+      <c r="E294" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers.agreement_reference</t>
+        </is>
+      </c>
+      <c r="F294" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="G294" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H294" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="inlineStr"/>
+      <c r="C295" s="9" t="inlineStr"/>
+      <c r="D295" s="10" t="inlineStr"/>
+      <c r="E295" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers.onboarding_queue</t>
+        </is>
+      </c>
+      <c r="F295" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+      <c r="G295" s="13" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="H295" s="10" t="inlineStr">
+        <is>
+          <t>Added</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="9" t="inlineStr">
+        <is>
+          <t>bd_onboarding_handovers</t>
+        </is>
+      </c>
+      <c r="B296" s="9" t="inlineStr"/>
+      <c r="C296" s="9" t="inlineStr"/>
+      <c r="D296" s="10" t="inlineStr"/>
+      <c r="E296" s="9" t="inlineStr">
+        <is>
           <t>bd_onboarding_handovers.idempotency_key</t>
         </is>
       </c>
-      <c r="F280" s="10" t="inlineStr">
+      <c r="F296" s="10" t="inlineStr">
         <is>
           <t>VARCHAR(100) · UNIQUE</t>
         </is>
       </c>
-      <c r="G280" s="13" t="inlineStr">
+      <c r="G296" s="13" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="H280" s="10" t="inlineStr">
+      <c r="H296" s="10" t="inlineStr">
         <is>
           <t>Mark Won retries return the same handover.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H280"/>
+  <autoFilter ref="A1:H296"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G280" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G296" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"As spec,Adjusted,Added,Missing"</formula1>
     </dataValidation>
   </dataValidations>
